--- a/Soluciones en Excel/VaR y L-VaR de divisas.xlsx
+++ b/Soluciones en Excel/VaR y L-VaR de divisas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samue\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/106876cc2438bd37/Desktop/TRABAJO/UNI/8VO SEMESTRE/ADMINISTRACION_RIESGOS/Soluciones en Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E5D3B4-C107-4B5B-B7EA-C2BE8427119C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{82E5D3B4-C107-4B5B-B7EA-C2BE8427119C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E45FA6A4-B81C-4627-A875-80CC8CF273BB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C7BAA134-55D3-451B-A976-9B052BE79902}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C7BAA134-55D3-451B-A976-9B052BE79902}"/>
   </bookViews>
   <sheets>
     <sheet name="FX" sheetId="1" r:id="rId1"/>
@@ -227,13 +227,13 @@
     <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -643,14 +643,14 @@
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
       <c r="L10" s="13"/>
-      <c r="M10" s="16" t="s">
+      <c r="M10" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="N10" s="16"/>
-      <c r="O10" s="15" t="s">
+      <c r="N10" s="17"/>
+      <c r="O10" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="P10" s="15"/>
+      <c r="P10" s="16"/>
     </row>
     <row r="11" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D11" s="9" t="s">
@@ -720,20 +720,20 @@
       </c>
     </row>
     <row r="14" spans="4:16" x14ac:dyDescent="0.25">
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17" t="s">
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="15" t="s">
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="L14" s="15"/>
+      <c r="L14" s="16"/>
       <c r="M14" s="7" t="s">
         <v>8</v>
       </c>
@@ -839,7 +839,7 @@
         <v>0.19147</v>
       </c>
       <c r="K17">
-        <f t="shared" ref="K16:K79" si="2">G17/G18-1</f>
+        <f t="shared" ref="K17:K79" si="2">G17/G18-1</f>
         <v>-1.9174341464741618E-3</v>
       </c>
       <c r="L17">
@@ -847,11 +847,11 @@
         <v>0</v>
       </c>
       <c r="M17" s="1">
-        <f t="shared" ref="M16:M79" si="3">SUMPRODUCT(K17:L17,$O$11:$P$11)</f>
+        <f t="shared" ref="M17:M79" si="3">SUMPRODUCT(K17:L17,$O$11:$P$11)</f>
         <v>-9.1415092055525016E-4</v>
       </c>
       <c r="N17" s="1">
-        <f t="shared" ref="N16:N79" si="4">(F17-E17)/G17</f>
+        <f t="shared" ref="N17:N79" si="4">(F17-E17)/G17</f>
         <v>2.2080184865850753E-4</v>
       </c>
       <c r="O17" s="1">
@@ -55844,7 +55844,7 @@
         <v>-1.484529321194783E-2</v>
       </c>
       <c r="M1296" s="1">
-        <f t="shared" ref="M1296:M1359" si="102">SUMPRODUCT(K1296:L1296,$O$11:$P$11)</f>
+        <f t="shared" ref="M1296:M1320" si="102">SUMPRODUCT(K1296:L1296,$O$11:$P$11)</f>
         <v>-1.1646720156877153E-2</v>
       </c>
       <c r="N1296" s="1">
